--- a/UNM_DOE_Menu_2026_Smartsheet.xlsx
+++ b/UNM_DOE_Menu_2026_Smartsheet.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,16 +26,29 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color indexed="8"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.5999938962981048"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -43,12 +56,31 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -414,131 +446,131 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y71"/>
+  <dimension ref="A1:Y61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>OMS Item Number</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>Item Name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>Restock</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>Print Group</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Show on Web</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>Main Price</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>DOE Price</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="2" t="inlineStr">
         <is>
           <t>Min Pre Order</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="2" t="inlineStr">
         <is>
           <t>Max Pre Order</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="2" t="inlineStr">
         <is>
           <t>Late Flag</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="2" t="inlineStr">
         <is>
           <t>DOE Min Order</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="2" t="inlineStr">
         <is>
           <t>DOE Max Order</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="2" t="inlineStr">
         <is>
           <t>Print Menu Tag</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="2" t="inlineStr">
         <is>
           <t>Print Label</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>Kitchen Prep Category</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="2" t="inlineStr">
         <is>
           <t>List Report Category</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="2" t="inlineStr">
         <is>
           <t>Component Name</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="2" t="inlineStr">
         <is>
           <t>Component Quantity Needed</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="2" t="inlineStr">
         <is>
           <t>Print Component Menu Tag</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="2" t="inlineStr">
         <is>
           <t>Print Component Label</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="2" t="inlineStr">
         <is>
           <t>Kitchen Prep Category - Component</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="2" t="inlineStr">
         <is>
           <t>List Report Category - Component</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="X1" s="2" t="inlineStr">
         <is>
           <t>Equipment Name</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="2" t="inlineStr">
         <is>
           <t>Equipment Quantity Needed</t>
         </is>
@@ -552,19 +584,100 @@
       </c>
     </row>
     <row r="3">
+      <c r="B3" t="n">
+        <v>2100882</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Classic Chips, Chile Con Queso &amp; Salsa Fresca</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FOOD-HOT</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>175</v>
+      </c>
+      <c r="H3" t="n">
+        <v>175</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>[Menu Section: Appetizers] All appetizers are served for a minimum of 10 guests unless noted otherwise</t>
+          <t>Warm Chile con Queso, House-Made Salsa, House-Made Tortilla Chips</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1 per 1 order</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Condiment</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>20015 - 1/2 Pan</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>1 per 1-99 orders</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="n">
-        <v>2100882</v>
+        <v>2101228</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Classic Chips, Chile Con Queso &amp; Salsa Fresca</t>
+          <t>Traditional Nacho Platter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -592,7 +705,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -612,32 +725,22 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hot Food</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Warm Chile con Queso, House-Made Salsa, House-Made Tortilla Chips</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>1 per 1 order</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>Condiment</t>
+          <t>Picadillo, Monterey Jack Cheese, Sour Cream, Avocado, Diced Tomatoes, Cilantro, Red Salsa, House-Made Tortilla Chips</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>20015 - 1/2 Pan</t>
+          <t>20124 - Claw Tong</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -648,11 +751,11 @@
     </row>
     <row r="5">
       <c r="B5" t="n">
-        <v>2101228</v>
+        <v>2102535</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Traditional Nacho Platter</t>
+          <t>The Chicken Tender &amp; Sauce Zone</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -671,16 +774,16 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="H5" t="n">
-        <v>175</v>
+        <v>210</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -691,7 +794,7 @@
         <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -710,12 +813,27 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Picadillo, Monterey Jack Cheese, Sour Cream, Avocado, Diced Tomatoes, Cilantro, Red Salsa, House-Made Tortilla Chips</t>
+          <t>Golden Brown Chicken Tenders, &amp; Sauce Bar: New Mexico Bang Bang Sauce, Signature Barbecue Sauce, Buttermilk Ranch Dressing, Spicy Buffalo Sauce</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>1 per 1 order</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Condiment</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>20124 - Claw Tong</t>
+          <t>20015 - 1/2 Pan</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -726,11 +844,11 @@
     </row>
     <row r="6">
       <c r="B6" t="n">
-        <v>2102535</v>
+        <v>230</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>The Chicken Tender &amp; Sauce Zone</t>
+          <t>Spicy Wings</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -749,10 +867,10 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="H6" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -769,7 +887,7 @@
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -788,7 +906,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Golden Brown Chicken Tenders, &amp; Sauce Bar: New Mexico Bang Bang Sauce, Signature Barbecue Sauce, Buttermilk Ranch Dressing, Spicy Buffalo Sauce</t>
+          <t>Traditional Spicy Buffalo Sauce, New Mexico Bang Bang Sauce, Buttermilk Ranch Dressing</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -808,129 +926,195 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>20015 - 1/2 Pan</t>
+          <t>20124 - Claw Tong</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
+          <t>2 per 1-99 orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>SNACKS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>14322</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Louie's Snack Attack</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>FOOD-SNACK</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>105</v>
+      </c>
+      <c r="H8" t="n">
+        <v>105</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>5</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>M&amp;M's Peanuts, Pretzels, Levy Snack Mix, Freshly Popped Popcorn</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>8900060 - Popcorn Bucket</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
           <t>1 per 1-99 orders</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="B7" t="n">
-        <v>230</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Spicy Wings</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>FOOD-HOT</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>220</v>
-      </c>
-      <c r="H7" t="n">
-        <v>220</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1</v>
-      </c>
-      <c r="J7" t="n">
+    <row r="9">
+      <c r="B9" t="n">
+        <v>3200010</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Salsa &amp; Guacamole Sampler</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>FOOD-SNACK</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>135</v>
+      </c>
+      <c r="H9" t="n">
+        <v>135</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="n">
         <v>5</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>15</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Hot Food</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Traditional Spicy Buffalo Sauce, New Mexico Bang Bang Sauce, Buttermilk Ranch Dressing</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Salsa, Fresh Guacamole, House-Made Tortilla Chips</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>1 per 1 order</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>Condiment</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>20124 - Claw Tong</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2 per 1-99 orders</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>SNACKS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>[Menu Section: Snacks] All snacks are served for a minimum of 10 to 12 guests unless noted otherwise</t>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>1 per 1-99 orders</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="n">
-        <v>14322</v>
+        <v>13333</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Louie's Snack Attack</t>
+          <t>Bottomless Freshly Popped Popcorn</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -949,10 +1133,10 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="H10" t="n">
-        <v>105</v>
+        <v>65</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
@@ -986,14 +1170,9 @@
           <t>Snack</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>M&amp;M's Peanuts, Pretzels, Levy Snack Mix, Freshly Popped Popcorn</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>8900060 - Popcorn Bucket</t>
+          <t>20142 - Cone Basket</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1004,11 +1183,11 @@
     </row>
     <row r="11">
       <c r="B11" t="n">
-        <v>3200010</v>
+        <v>164</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Salsa &amp; Guacamole Sampler</t>
+          <t>Snack Mix</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1027,10 +1206,10 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="H11" t="n">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
@@ -1059,29 +1238,14 @@
           <t>N</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Salsa, Fresh Guacamole, House-Made Tortilla Chips</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>1 per 1 order</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Condiment</t>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Snack</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>20124 - Claw Tong</t>
+          <t>8900795 - Large Bath Tub Bowl</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1092,11 +1256,11 @@
     </row>
     <row r="12">
       <c r="B12" t="n">
-        <v>13333</v>
+        <v>163</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bottomless Freshly Popped Popcorn</t>
+          <t>Pretzel Twists</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1115,10 +1279,10 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H12" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="I12" t="n">
         <v>1</v>
@@ -1144,7 +1308,7 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1154,7 +1318,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>20142 - Cone Basket</t>
+          <t>8900795 - Large Bath Tub Bowl</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1165,11 +1329,11 @@
     </row>
     <row r="13">
       <c r="B13" t="n">
-        <v>164</v>
+        <v>125</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Snack Mix</t>
+          <t>Dry-Roasted Peanuts</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1238,11 +1402,11 @@
     </row>
     <row r="14">
       <c r="B14" t="n">
-        <v>163</v>
+        <v>6651</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Pretzel Twists</t>
+          <t>Gourmet Cookies &amp; Brownies</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1252,7 +1416,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>FOOD-SNACK</t>
+          <t>FOOD-COLD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1261,16 +1425,16 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="H14" t="n">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1281,7 +1445,7 @@
         <v>1</v>
       </c>
       <c r="M14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1290,17 +1454,22 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Snack</t>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Cold Food</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>Assorted Gourmet Cookies &amp; Decadent Brownies; Serves 10 guests</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>8900795 - Large Bath Tub Bowl</t>
+          <t>20130 - Tong</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -1310,92 +1479,107 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
-        <v>125</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Dry-Roasted Peanuts</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>FOOD-SNACK</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>45</v>
-      </c>
-      <c r="H15" t="n">
-        <v>45</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5</v>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L15" t="n">
-        <v>1</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Snack</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>8900795 - Large Bath Tub Bowl</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>HOT DOGS/SAUSAGES</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>3000328</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Lobo Dogs</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>FOOD-HOT</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>180</v>
+      </c>
+      <c r="H16" t="n">
+        <v>180</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
+        <v>15</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>15</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>Grilled Hot Dogs, Traditional Condiments; 2 DOGS PER GUEST</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1 per 1 order</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Condiment</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>20015 - 1/2 Pan</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
         <is>
           <t>1 per 1-99 orders</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>DESSERTS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>6651</v>
+        <v>99216</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gourmet Cookies &amp; Brownies</t>
+          <t>Upgrade your Lobo Dogs: Frito Pie Red Chile</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1405,99 +1589,159 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FOOD-COLD</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="G17" t="n">
+        <v>40</v>
+      </c>
+      <c r="H17" t="n">
+        <v>40</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="n">
+        <v>100</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>Add-on upgrade for Lobo Dogs</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>2303580</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Louie's Legendary Frito Pie</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>FOOD-HOT</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
         <v>170</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H18" t="n">
         <v>170</v>
       </c>
-      <c r="I17" t="n">
-        <v>1</v>
-      </c>
-      <c r="J17" t="n">
-        <v>10</v>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M17" t="n">
-        <v>10</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Cold Food</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Assorted Gourmet Cookies &amp; Decadent Brownies; Serves 10 guests</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>20130 - Tong</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
+      <c r="I18" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" t="n">
+        <v>10</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" t="n">
+        <v>10</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>Chile, Fritos Corn Chips, Shredded Lettuce, Tomatoes, Diced Onions, Shredded Cheese</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1 per 1 order</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Snack</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>20015 - 1/2 Pan</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
         <is>
           <t>1 per 1-99 orders</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>HOT DOGS/SAUSAGES</t>
-        </is>
-      </c>
-    </row>
     <row r="19">
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>[Menu Section: Dogs &amp; More] All dogs &amp; more are served for a minimum of 10 guests unless noted otherwise</t>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BEV-SOFT DRINKS</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
-        <v>3000328</v>
+        <v>904</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lobo Dogs</t>
+          <t>Pepsi</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>FOOD-HOT</t>
+          <t>BEV-NA BEV</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1506,16 +1750,16 @@
         </is>
       </c>
       <c r="G20" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="H20" t="n">
-        <v>180</v>
+        <v>45</v>
       </c>
       <c r="I20" t="n">
         <v>1</v>
       </c>
       <c r="J20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1526,89 +1770,65 @@
         <v>1</v>
       </c>
       <c r="M20" t="n">
-        <v>15</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>20</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
           <t>N</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Grilled Hot Dogs, Traditional Condiments; 2 DOGS PER GUEST</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>1 per 1 order</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Condiment</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>20015 - 1/2 Pan</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>1 per 1-99 orders</t>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>Liquor</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="n">
-        <v>99216</v>
+        <v>4700138</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Upgrade your Lobo Dogs: Frito Pie Red Chile</t>
+          <t>Pepsi Zero Sugar</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>BEV-NA BEV</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="H21" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="I21" t="n">
         <v>1</v>
       </c>
       <c r="J21" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L21" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" t="n">
+        <v>10</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -1620,29 +1840,29 @@
           <t>N</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Add-on upgrade for Lobo Dogs</t>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>Liquor</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="n">
-        <v>2303580</v>
+        <v>4700623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Louie's Legendary Frito Pie</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>FOOD-HOT</t>
+          <t>BEV-NA BEV</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1651,16 +1871,16 @@
         </is>
       </c>
       <c r="G22" t="n">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="H22" t="n">
-        <v>170</v>
+        <v>45</v>
       </c>
       <c r="I22" t="n">
         <v>1</v>
       </c>
       <c r="J22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -1671,7 +1891,7 @@
         <v>1</v>
       </c>
       <c r="M22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -1683,58 +1903,145 @@
           <t>N</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>Chile, Fritos Corn Chips, Shredded Lettuce, Tomatoes, Diced Onions, Shredded Cheese</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>1 per 1 order</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Snack</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>20015 - 1/2 Pan</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>1 per 1-99 orders</t>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>Liquor</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>BEV-SOFT DRINKS</t>
+      <c r="B23" t="n">
+        <v>918</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Mug Root Beer</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>BEV-NA BEV</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>45</v>
+      </c>
+      <c r="H23" t="n">
+        <v>45</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1</v>
+      </c>
+      <c r="J23" t="n">
+        <v>20</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" t="n">
+        <v>20</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>Liquor</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>[Menu Section: Chill - Soft Drinks] Sold by the 6-pack unless otherwise noted</t>
+      <c r="B24" t="n">
+        <v>4700098</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Pure Leaf Iced Tea Lemon 18.5oz</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>BEV-NA BEV</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>65</v>
+      </c>
+      <c r="H24" t="n">
+        <v>65</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>20</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" t="n">
+        <v>20</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Liquor</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" t="n">
-        <v>904</v>
+        <v>4700055</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pepsi</t>
+          <t>Pure Leaf Sweet Tea 18.5oz</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1753,16 +2060,16 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H25" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
       </c>
       <c r="J25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -1773,7 +2080,12 @@
         <v>1</v>
       </c>
       <c r="M25" t="n">
-        <v>20</v>
+        <v>10</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
@@ -1788,11 +2100,11 @@
     </row>
     <row r="26">
       <c r="B26" t="n">
-        <v>4700138</v>
+        <v>4700056</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pepsi Zero Sugar</t>
+          <t>Pure Leaf Unsweetened Black Tea 18.5oz</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1811,10 +2123,10 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="H26" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -1850,75 +2162,19 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="n">
-        <v>4700623</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Starry</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>BEV-NA BEV</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>45</v>
-      </c>
-      <c r="H27" t="n">
-        <v>45</v>
-      </c>
-      <c r="I27" t="n">
-        <v>1</v>
-      </c>
-      <c r="J27" t="n">
-        <v>15</v>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>1</v>
-      </c>
-      <c r="M27" t="n">
-        <v>15</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Liquor</t>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BEV-WATER</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" t="n">
-        <v>918</v>
+        <v>958</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mug Root Beer</t>
+          <t>Aquafina Bottled Water</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1937,116 +2193,116 @@
         </is>
       </c>
       <c r="G28" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="H28" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="I28" t="n">
         <v>1</v>
       </c>
       <c r="J28" t="n">
+        <v>99</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L28" t="n">
+        <v>1</v>
+      </c>
+      <c r="M28" t="n">
+        <v>99</v>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Liquor</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>970</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Schweppes Club Soda</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>BEV-NA BEV</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>25</v>
+      </c>
+      <c r="H29" t="n">
+        <v>25</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
         <v>20</v>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>1</v>
-      </c>
-      <c r="M28" t="n">
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L29" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" t="n">
         <v>20</v>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Liquor</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>BEV-WATER</t>
-        </is>
-      </c>
-    </row>
     <row r="30">
-      <c r="B30" t="n">
-        <v>958</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Aquafina Bottled Water</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>BEV-NA BEV</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>40</v>
-      </c>
-      <c r="H30" t="n">
-        <v>40</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1</v>
-      </c>
-      <c r="J30" t="n">
-        <v>99</v>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" t="n">
-        <v>99</v>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Liquor</t>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BAR MIXERS</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>970</v>
+        <v>5000178</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Schweppes Club Soda</t>
+          <t>Lemon Wedges</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2056,67 +2312,128 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
+          <t>FOOD-COLD</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>20</v>
+      </c>
+      <c r="H31" t="n">
+        <v>20</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="n">
+        <v>15</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L31" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" t="n">
+        <v>15</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Liquor</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>8900742 - Bar Tong</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>1 per 1-99 orders</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>5000134</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Lime Wedges</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>BEV-NA BEV</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>25</v>
-      </c>
-      <c r="H31" t="n">
-        <v>25</v>
-      </c>
-      <c r="I31" t="n">
-        <v>1</v>
-      </c>
-      <c r="J31" t="n">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
         <v>20</v>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>1</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="H32" t="n">
         <v>20</v>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Liquor</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>BAR MIXERS</t>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>10</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L32" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" t="n">
+        <v>10</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>5000178</v>
+        <v>5000180</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Lemon Wedges</t>
+          <t>Orange Wedges</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2184,70 +2501,19 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="n">
-        <v>5000134</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Lime Wedges</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>BEV-NA BEV</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>20</v>
-      </c>
-      <c r="H34" t="n">
-        <v>20</v>
-      </c>
-      <c r="I34" t="n">
-        <v>1</v>
-      </c>
-      <c r="J34" t="n">
-        <v>10</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" t="n">
-        <v>10</v>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>N</t>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BEER-DOMESTIC</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>5000180</v>
+        <v>704</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Orange Wedges</t>
+          <t>Bud Light</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2257,7 +2523,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FOOD-COLD</t>
+          <t>BEV-BEER</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2266,16 +2532,16 @@
         </is>
       </c>
       <c r="G35" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="H35" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="I35" t="n">
         <v>1</v>
       </c>
       <c r="J35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2286,12 +2552,7 @@
         <v>1</v>
       </c>
       <c r="M35" t="n">
-        <v>15</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
+        <v>10</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2303,31 +2564,72 @@
           <t>Liquor</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>8900742 - Bar Tong</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>1 per 1-99 orders</t>
-        </is>
-      </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>BEV-SOFT DRINKS</t>
+      <c r="B36" t="n">
+        <v>1730</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Michelob ULTRA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>BEV-BEER</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>60</v>
+      </c>
+      <c r="H36" t="n">
+        <v>60</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>10</v>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" t="n">
+        <v>10</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>Liquor</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="n">
-        <v>4700098</v>
+        <v>6001392</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pure Leaf Iced Tea Lemon 18.5oz</t>
+          <t>Marble Double White</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2337,7 +2639,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>BEV-NA BEV</t>
+          <t>BEV-BEER</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2346,10 +2648,10 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="H37" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="I37" t="n">
         <v>1</v>
@@ -2386,11 +2688,11 @@
     </row>
     <row r="38">
       <c r="B38" t="n">
-        <v>4700055</v>
+        <v>6001205</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Pure Leaf Sweet Tea 18.5oz</t>
+          <t>Classic Bundle</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2400,7 +2702,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>BEV-NA BEV</t>
+          <t>BEV-BEER</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2409,10 +2711,10 @@
         </is>
       </c>
       <c r="G38" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="H38" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="I38" t="n">
         <v>1</v>
@@ -2422,7 +2724,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>N</t>
         </is>
       </c>
       <c r="L38" t="n">
@@ -2444,16 +2746,21 @@
       <c r="Q38" t="inlineStr">
         <is>
           <t>Liquor</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Bud Light, Michelob ULTRA, Estrella Jalisco; 85 PER 6-PACK</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="n">
-        <v>4700056</v>
+        <v>6003196</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pure Leaf Unsweetened Black Tea 18.5oz</t>
+          <t>505 Craft Collection</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2463,7 +2770,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>BEV-NA BEV</t>
+          <t>BEV-BEER</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2472,10 +2779,10 @@
         </is>
       </c>
       <c r="G39" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="H39" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="I39" t="n">
         <v>1</v>
@@ -2509,28 +2816,44 @@
           <t>Liquor</t>
         </is>
       </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>A Microbrew Bundle from Local Breweries: Santa Fe Brewing Co. 7K IPA, Teller Lobo Cherry Limeade, NÜTRL Vodka Seltzer; 85 PER 6-PACK</t>
+        </is>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>BEER-DOMESTIC</t>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Southwest Select</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>85</v>
+      </c>
+      <c r="H40" t="n">
+        <v>85</v>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>Modelo Especial, Michelob ULTRA; 85 PER 6-PACK</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="R41" t="inlineStr">
-        <is>
-          <t>[Menu Section: Beers, Ales &amp; Alternatives] Sold by the 6-pack unless otherwise noted</t>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BEER-IMPORTED</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" t="n">
-        <v>704</v>
+        <v>77940</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Bud Light</t>
+          <t>Dos Equis Lager</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2549,10 +2872,10 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="H42" t="n">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="I42" t="n">
         <v>1</v>
@@ -2583,212 +2906,182 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="n">
-        <v>1730</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Michelob ULTRA</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>BEER-RTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="n">
+        <v>6002607</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>NÜTRL Vodka Seltzer</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
         <is>
           <t>BEV-BEER</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G43" t="n">
-        <v>60</v>
-      </c>
-      <c r="H43" t="n">
-        <v>60</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" t="n">
-        <v>10</v>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>1</v>
-      </c>
-      <c r="M43" t="n">
-        <v>10</v>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q43" t="inlineStr">
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>85</v>
+      </c>
+      <c r="H44" t="n">
+        <v>85</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="n">
+        <v>10</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" t="n">
+        <v>10</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Liquor</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>BEER-IMPORTED</t>
-        </is>
-      </c>
-    </row>
     <row r="45">
-      <c r="B45" t="n">
-        <v>77940</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Dos Equis Lager</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>BEV-BEER</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>85</v>
-      </c>
-      <c r="H45" t="n">
-        <v>85</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" t="n">
-        <v>10</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" t="n">
-        <v>10</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>WINE-SPARKLING</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="n">
+        <v>3700127</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Gruet Brut</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>BEV-WINE</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>110</v>
+      </c>
+      <c r="H46" t="n">
+        <v>110</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="n">
+        <v>10</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>10</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
         <is>
           <t>Liquor</t>
         </is>
       </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>BEER-DOMESTIC</t>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Sparkling</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="n">
-        <v>6001392</v>
-      </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Marble Double White</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>BEV-BEER</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Y</t>
+          <t>Cavit</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="H47" t="n">
-        <v>85</v>
-      </c>
-      <c r="I47" t="n">
-        <v>1</v>
-      </c>
-      <c r="J47" t="n">
-        <v>20</v>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L47" t="n">
-        <v>1</v>
-      </c>
-      <c r="M47" t="n">
-        <v>20</v>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q47" t="inlineStr">
-        <is>
-          <t>Liquor</t>
+        <v>110</v>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Sparkling</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BEER-RTD</t>
+          <t>WINE-WHITE</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" t="n">
-        <v>6002607</v>
+        <v>3800357</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>NÜTRL Vodka Seltzer</t>
+          <t>Woodbridge Pinot Grigio</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2798,7 +3091,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>BEV-BEER</t>
+          <t>BEV-WINE</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2807,10 +3100,10 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="H49" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="I49" t="n">
         <v>1</v>
@@ -2846,26 +3139,128 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>BEER-DOMESTIC</t>
+      <c r="B50" t="n">
+        <v>16090</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Chateau Ste. Michelle Riesling</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>BEV-WINE</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>100</v>
+      </c>
+      <c r="H50" t="n">
+        <v>100</v>
+      </c>
+      <c r="I50" t="n">
+        <v>1</v>
+      </c>
+      <c r="J50" t="n">
+        <v>10</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" t="n">
+        <v>10</v>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Liquor</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>[Menu Section: Mix &amp; Match Bundles] Our beer bundle packages include an assorted 6-pack of different beers; 85 PER 6-PACK</t>
+      <c r="B51" t="n">
+        <v>13659</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Kim Crawford Sauvignon Blanc</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>BEV-WINE</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>130</v>
+      </c>
+      <c r="H51" t="n">
+        <v>130</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1</v>
+      </c>
+      <c r="J51" t="n">
+        <v>10</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>10</v>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>Liquor</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" t="n">
-        <v>6001205</v>
+        <v>12000</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Classic Bundle</t>
+          <t>Kendall-Jackson Chardonnay</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2875,7 +3270,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>BEV-BEER</t>
+          <t>BEV-WINE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2884,10 +3279,10 @@
         </is>
       </c>
       <c r="G52" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="H52" t="n">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="I52" t="n">
         <v>1</v>
@@ -2897,7 +3292,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="L52" t="n">
@@ -2906,11 +3301,6 @@
       <c r="M52" t="n">
         <v>10</v>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
       <c r="O52" t="inlineStr">
         <is>
           <t>N</t>
@@ -2919,21 +3309,16 @@
       <c r="Q52" t="inlineStr">
         <is>
           <t>Liquor</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>Bud Light, Michelob ULTRA, Estrella Jalisco</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" t="n">
-        <v>6003196</v>
+        <v>11198</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>505 Craft Collection</t>
+          <t>Woodbridge Chardonnay</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2943,7 +3328,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>BEV-BEER</t>
+          <t>BEV-WINE</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2952,10 +3337,10 @@
         </is>
       </c>
       <c r="G53" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="H53" t="n">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="I53" t="n">
         <v>1</v>
@@ -2989,44 +3374,79 @@
           <t>Liquor</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>A Microbrew Bundle from Local Breweries: Santa Fe Brewing Co. 7K IPA, Teller Lobo Cherry Limeade, NÜTRL Vodka Seltzer</t>
-        </is>
-      </c>
     </row>
     <row r="54">
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Southwest Select</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>85</v>
-      </c>
-      <c r="H54" t="n">
-        <v>85</v>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>Modelo Especial, Michelob ULTRA</t>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>WINE-RED</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>WINE-SPARKLING</t>
+      <c r="B55" t="n">
+        <v>3900152</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Meiomi Pinot Noir</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>BEV-WINE</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>115</v>
+      </c>
+      <c r="H55" t="n">
+        <v>115</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1</v>
+      </c>
+      <c r="J55" t="n">
+        <v>10</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>1</v>
+      </c>
+      <c r="M55" t="n">
+        <v>10</v>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>Liquor</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" t="n">
-        <v>3700127</v>
+        <v>3900724</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Gruet Brut</t>
+          <t>Emmolo Merlot</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3045,16 +3465,16 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>110</v>
+        <v>195</v>
       </c>
       <c r="H56" t="n">
-        <v>110</v>
+        <v>195</v>
       </c>
       <c r="I56" t="n">
         <v>1</v>
       </c>
       <c r="J56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -3065,7 +3485,7 @@
         <v>1</v>
       </c>
       <c r="M56" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -3082,44 +3502,140 @@
           <t>Liquor</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>Sparkling</t>
-        </is>
-      </c>
     </row>
     <row r="57">
+      <c r="B57" t="n">
+        <v>11194</v>
+      </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cavit</t>
+          <t>Woodbridge Merlot</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>BEV-WINE</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Y</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>110</v>
+        <v>60</v>
       </c>
       <c r="H57" t="n">
-        <v>110</v>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>Sparkling</t>
+        <v>60</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="n">
+        <v>10</v>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L57" t="n">
+        <v>1</v>
+      </c>
+      <c r="M57" t="n">
+        <v>10</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>Liquor</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>WINE-WHITE</t>
+      <c r="B58" t="n">
+        <v>3901227</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Decoy by Duckhorn Cabernet Sauvignon</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>BEV-WINE</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>190</v>
+      </c>
+      <c r="H58" t="n">
+        <v>190</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>10</v>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="L58" t="n">
+        <v>1</v>
+      </c>
+      <c r="M58" t="n">
+        <v>10</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>Liquor</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" t="n">
-        <v>3800357</v>
+        <v>16029</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Woodbridge Pinot Grigio</t>
+          <t>Louis Martini Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3138,10 +3654,10 @@
         </is>
       </c>
       <c r="G59" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="H59" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
@@ -3159,11 +3675,6 @@
       </c>
       <c r="M59" t="n">
         <v>10</v>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3178,11 +3689,11 @@
     </row>
     <row r="60">
       <c r="B60" t="n">
-        <v>16090</v>
+        <v>11189</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chateau Ste. Michelle Riesling</t>
+          <t>Woodbridge Cabernet Sauvignon</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3201,10 +3712,10 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="H60" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="I60" t="n">
         <v>1</v>
@@ -3222,6 +3733,11 @@
       </c>
       <c r="M60" t="n">
         <v>10</v>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -3236,11 +3752,11 @@
     </row>
     <row r="61">
       <c r="B61" t="n">
-        <v>13659</v>
+        <v>3900051</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Kim Crawford Sauvignon Blanc</t>
+          <t>The Prisoner Red Blend</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -3259,16 +3775,16 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>130</v>
+        <v>280</v>
       </c>
       <c r="H61" t="n">
-        <v>130</v>
+        <v>280</v>
       </c>
       <c r="I61" t="n">
         <v>1</v>
       </c>
       <c r="J61" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -3279,7 +3795,12 @@
         <v>1</v>
       </c>
       <c r="M61" t="n">
-        <v>10</v>
+        <v>20</v>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -3287,565 +3808,6 @@
         </is>
       </c>
       <c r="Q61" t="inlineStr">
-        <is>
-          <t>Liquor</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" t="n">
-        <v>12000</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Kendall-Jackson Chardonnay</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>BEV-WINE</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G62" t="n">
-        <v>125</v>
-      </c>
-      <c r="H62" t="n">
-        <v>125</v>
-      </c>
-      <c r="I62" t="n">
-        <v>1</v>
-      </c>
-      <c r="J62" t="n">
-        <v>10</v>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>1</v>
-      </c>
-      <c r="M62" t="n">
-        <v>10</v>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q62" t="inlineStr">
-        <is>
-          <t>Liquor</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" t="n">
-        <v>11198</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Woodbridge Chardonnay</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>BEV-WINE</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G63" t="n">
-        <v>60</v>
-      </c>
-      <c r="H63" t="n">
-        <v>60</v>
-      </c>
-      <c r="I63" t="n">
-        <v>1</v>
-      </c>
-      <c r="J63" t="n">
-        <v>10</v>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L63" t="n">
-        <v>1</v>
-      </c>
-      <c r="M63" t="n">
-        <v>10</v>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>Liquor</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>WINE-RED</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="B65" t="n">
-        <v>3900152</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Meiomi Pinot Noir</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>BEV-WINE</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>115</v>
-      </c>
-      <c r="H65" t="n">
-        <v>115</v>
-      </c>
-      <c r="I65" t="n">
-        <v>1</v>
-      </c>
-      <c r="J65" t="n">
-        <v>10</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L65" t="n">
-        <v>1</v>
-      </c>
-      <c r="M65" t="n">
-        <v>10</v>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>Liquor</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="B66" t="n">
-        <v>3900724</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Emmolo Merlot</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>BEV-WINE</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>195</v>
-      </c>
-      <c r="H66" t="n">
-        <v>195</v>
-      </c>
-      <c r="I66" t="n">
-        <v>1</v>
-      </c>
-      <c r="J66" t="n">
-        <v>20</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L66" t="n">
-        <v>1</v>
-      </c>
-      <c r="M66" t="n">
-        <v>20</v>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q66" t="inlineStr">
-        <is>
-          <t>Liquor</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" t="n">
-        <v>11194</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Woodbridge Merlot</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>BEV-WINE</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>60</v>
-      </c>
-      <c r="H67" t="n">
-        <v>60</v>
-      </c>
-      <c r="I67" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" t="n">
-        <v>10</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L67" t="n">
-        <v>1</v>
-      </c>
-      <c r="M67" t="n">
-        <v>10</v>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
-        <is>
-          <t>Liquor</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="B68" t="n">
-        <v>3901227</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Decoy by Duckhorn Cabernet Sauvignon</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>BEV-WINE</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
-        <v>190</v>
-      </c>
-      <c r="H68" t="n">
-        <v>190</v>
-      </c>
-      <c r="I68" t="n">
-        <v>1</v>
-      </c>
-      <c r="J68" t="n">
-        <v>10</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L68" t="n">
-        <v>1</v>
-      </c>
-      <c r="M68" t="n">
-        <v>10</v>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q68" t="inlineStr">
-        <is>
-          <t>Liquor</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" t="n">
-        <v>16029</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Louis Martini Cabernet Sauvignon</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>BEV-WINE</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>100</v>
-      </c>
-      <c r="H69" t="n">
-        <v>100</v>
-      </c>
-      <c r="I69" t="n">
-        <v>1</v>
-      </c>
-      <c r="J69" t="n">
-        <v>10</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L69" t="n">
-        <v>1</v>
-      </c>
-      <c r="M69" t="n">
-        <v>10</v>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q69" t="inlineStr">
-        <is>
-          <t>Liquor</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" t="n">
-        <v>11189</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Woodbridge Cabernet Sauvignon</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>BEV-WINE</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
-        <v>60</v>
-      </c>
-      <c r="H70" t="n">
-        <v>60</v>
-      </c>
-      <c r="I70" t="n">
-        <v>1</v>
-      </c>
-      <c r="J70" t="n">
-        <v>10</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L70" t="n">
-        <v>1</v>
-      </c>
-      <c r="M70" t="n">
-        <v>10</v>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q70" t="inlineStr">
-        <is>
-          <t>Liquor</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" t="n">
-        <v>3900051</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>The Prisoner Red Blend</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>BEV-WINE</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="G71" t="n">
-        <v>280</v>
-      </c>
-      <c r="H71" t="n">
-        <v>280</v>
-      </c>
-      <c r="I71" t="n">
-        <v>1</v>
-      </c>
-      <c r="J71" t="n">
-        <v>20</v>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="L71" t="n">
-        <v>1</v>
-      </c>
-      <c r="M71" t="n">
-        <v>20</v>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="Q71" t="inlineStr">
         <is>
           <t>Liquor</t>
         </is>
